--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.29316312655842</v>
+        <v>8.497639008065743</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42992848443916</v>
+        <v>2.019863378721364</v>
       </c>
       <c r="E2" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F2" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.94168384933214</v>
+        <v>7.628023625516474</v>
       </c>
       <c r="D3" t="n">
-        <v>8.10205023255803</v>
+        <v>1.31658316279068</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F3" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.22566650007793</v>
+        <v>9.136670806262664</v>
       </c>
       <c r="D4" t="n">
-        <v>37.79430410827101</v>
+        <v>6.14157441759404</v>
       </c>
       <c r="E4" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F4" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.35967343079618</v>
+        <v>3.308446932504379</v>
       </c>
       <c r="D5" t="n">
-        <v>12.495667335581</v>
+        <v>2.030545942031912</v>
       </c>
       <c r="E5" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F5" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.55522423843308</v>
+        <v>4.152723938745375</v>
       </c>
       <c r="D6" t="n">
-        <v>7.566372975210778</v>
+        <v>1.229535608471751</v>
       </c>
       <c r="E6" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F6" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.46191162229841</v>
+        <v>7.062560638623491</v>
       </c>
       <c r="D7" t="n">
-        <v>40.02866902188219</v>
+        <v>6.504658716055856</v>
       </c>
       <c r="E7" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F7" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.51241486538673</v>
+        <v>5.120767415625344</v>
       </c>
       <c r="D8" t="n">
-        <v>29.53563772950532</v>
+        <v>4.799541131044614</v>
       </c>
       <c r="E8" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F8" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.81499579172746</v>
+        <v>5.169936816155712</v>
       </c>
       <c r="D9" t="n">
-        <v>17.29449450396024</v>
+        <v>2.81035535689354</v>
       </c>
       <c r="E9" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F9" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.6176924831767</v>
+        <v>4.975375028516214</v>
       </c>
       <c r="D10" t="n">
-        <v>24.75883680627989</v>
+        <v>4.023310981020483</v>
       </c>
       <c r="E10" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F10" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.11471690686008</v>
+        <v>2.131141497364764</v>
       </c>
       <c r="D11" t="n">
-        <v>11.9151251408335</v>
+        <v>1.936207835385443</v>
       </c>
       <c r="E11" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F11" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.12900107210811</v>
+        <v>4.570962674217568</v>
       </c>
       <c r="D12" t="n">
-        <v>22.7205594002486</v>
+        <v>3.692090902540398</v>
       </c>
       <c r="E12" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F12" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>2.287249443582194</v>
+        <v>0.3716780345821065</v>
       </c>
       <c r="D13" t="n">
-        <v>2.895437686162413</v>
+        <v>0.4705086240013922</v>
       </c>
       <c r="E13" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F13" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.64132908559637</v>
+        <v>2.704215976409411</v>
       </c>
       <c r="D14" t="n">
-        <v>13.0669606124368</v>
+        <v>2.12338109952098</v>
       </c>
       <c r="E14" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F14" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>59.27398821584681</v>
+        <v>9.632023085075108</v>
       </c>
       <c r="D15" t="n">
-        <v>83.32200030705599</v>
+        <v>13.5398250498966</v>
       </c>
       <c r="E15" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F15" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>4.001674139540501</v>
+        <v>0.6502720476753315</v>
       </c>
       <c r="D16" t="n">
-        <v>36.45549226860356</v>
+        <v>5.924017493648078</v>
       </c>
       <c r="E16" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F16" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>46.32437587732507</v>
+        <v>7.527711080065325</v>
       </c>
       <c r="D17" t="n">
-        <v>82.49349233034948</v>
+        <v>13.40519250368179</v>
       </c>
       <c r="E17" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F17" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>13.85346968171593</v>
+        <v>2.251188823278838</v>
       </c>
       <c r="D18" t="n">
-        <v>60.70697826662782</v>
+        <v>9.864883968327021</v>
       </c>
       <c r="E18" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F18" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>27.38988278566278</v>
+        <v>4.450855952670202</v>
       </c>
       <c r="D19" t="n">
-        <v>87.67414846966967</v>
+        <v>14.24704912632132</v>
       </c>
       <c r="E19" t="n">
-        <v>16.78009367886269</v>
+        <v>2.726765222815188</v>
       </c>
       <c r="F19" t="n">
-        <v>26.99127657902817</v>
+        <v>4.386082444092077</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
